--- a/DXY_Price_Gap_Theory_2026.xlsx
+++ b/DXY_Price_Gap_Theory_2026.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,14 +39,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007F6000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,18 +65,6 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,12 +99,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -490,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -589,15 +565,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22.5723</v>
+        <v>98.7667</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-76.25</v>
+        <v>-0.05</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -610,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -643,15 +619,15 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22.5546</v>
+        <v>98.71769999999999</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-76.22</v>
+        <v>-0.05</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -664,7 +640,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -697,15 +673,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22.5406</v>
+        <v>98.4674</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-75.98999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -718,7 +694,7 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -751,15 +727,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22.5971</v>
+        <v>98.682</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-76.15000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -772,7 +748,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -805,15 +781,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22.5566</v>
+        <v>99.02809999999999</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-76.54000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -826,7 +802,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -859,15 +835,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.5524</v>
+        <v>98.7957</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-76.31999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -880,7 +856,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -913,15 +889,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22.5323</v>
+        <v>99.4252</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-76.98999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -933,8 +909,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0.2</v>
+      <c r="J8" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -967,15 +943,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22.4879</v>
+        <v>99.5034</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-77.11</v>
+        <v>-0.1</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -987,8 +963,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0.19</v>
+      <c r="J9" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1021,15 +997,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22.4637</v>
+        <v>99.2376</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-76.88</v>
+        <v>-0.1</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -1041,8 +1017,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0.19</v>
+      <c r="J10" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1075,15 +1051,15 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.4958</v>
+        <v>99.5091</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-77.12</v>
+        <v>-0.11</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -1095,8 +1071,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>0.17</v>
+      <c r="J11" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1129,15 +1105,15 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22.4225</v>
+        <v>98.9472</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-76.64</v>
+        <v>-0.11</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1149,8 +1125,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.16</v>
+      <c r="J12" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1183,15 +1159,15 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22.4146</v>
+        <v>98.937</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-76.65000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -1203,8 +1179,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>0.18</v>
+      <c r="J13" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1237,15 +1213,15 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22.3868</v>
+        <v>98.6815</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-76.42</v>
+        <v>-0.13</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1257,8 +1233,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0.18</v>
+      <c r="J14" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1291,15 +1267,15 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>22.4007</v>
+        <v>98.76560000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-76.5</v>
+        <v>-0.13</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -1311,8 +1287,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0.19</v>
+      <c r="J15" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1345,15 +1321,15 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22.3948</v>
+        <v>98.57429999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-76.31999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1365,8 +1341,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0.18</v>
+      <c r="J16" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1399,15 +1375,15 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22.401</v>
+        <v>98.6596</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-76.40000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -1419,8 +1395,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>0.18</v>
+      <c r="J17" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1453,15 +1429,15 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>22.4166</v>
+        <v>98.5757</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-76.31</v>
+        <v>-0.15</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1473,8 +1449,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0.17</v>
+      <c r="J18" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1507,15 +1483,15 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>22.4876</v>
+        <v>99.3716</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-77.04000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1527,8 +1503,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>0.19</v>
+      <c r="J19" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1561,15 +1537,15 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>22.4935</v>
+        <v>99.33839999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-77.01000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1558,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1615,15 +1591,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>22.5044</v>
+        <v>99.3609</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-77.03</v>
+        <v>-0.17</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1636,7 +1612,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1669,15 +1645,15 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22.5434</v>
+        <v>99.6386</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-77.27</v>
+        <v>-0.17</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1689,8 +1665,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0.21</v>
+      <c r="J22" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1723,15 +1699,15 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>22.5512</v>
+        <v>99.6741</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-77.31</v>
+        <v>-0.19</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1743,8 +1719,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>0.21</v>
+      <c r="J23" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1777,15 +1753,15 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>22.5338</v>
+        <v>99.4965</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-77.16</v>
+        <v>-0.19</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1798,7 +1774,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1822,24 +1798,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>22.528</v>
+        <v>99.4832</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-77.15000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1851,9 +1827,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -1868,32 +1842,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>99.38</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>22.536</v>
+        <v>99.55840000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-76.84</v>
+        <v>-0.2</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -1905,9 +1879,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -1922,32 +1894,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>99.76000000000001</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22.5596</v>
+        <v>99.2972</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-77.2</v>
+        <v>-0.21</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -1974,32 +1946,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>99.51000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.12</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22.5409</v>
+        <v>99.4982</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-76.97</v>
+        <v>-0.22</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -2026,32 +1998,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>99.72</v>
+        <v>99.73</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>+0.18</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.5627</v>
+        <v>99.5067</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-77.16</v>
+        <v>-0.22</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -2078,32 +2050,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>99.75</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22.6142</v>
+        <v>99.473</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-77.14</v>
+        <v>-0.24</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -2130,32 +2102,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>99.73</v>
+        <v>100.71</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+0.18</t>
+          <t>+0.03</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22.5364</v>
+        <v>100.4573</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-77.19</v>
+        <v>-0.25</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -2182,32 +2154,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>99.70999999999999</v>
+        <v>101.21</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22.536</v>
+        <v>100.9425</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-77.17</v>
+        <v>-0.27</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -2234,32 +2206,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100.71</v>
+        <v>101.34</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>22.5577</v>
+        <v>101.0656</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-78.15000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -2286,32 +2258,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>101.21</v>
+        <v>101.26</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22.621</v>
+        <v>100.9822</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-78.59</v>
+        <v>-0.28</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -2338,32 +2310,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>101.34</v>
+        <v>101.25</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>22.6459</v>
+        <v>100.9661</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-78.69</v>
+        <v>-0.28</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2390,32 +2362,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>101.26</v>
+        <v>100.92</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22.6363</v>
+        <v>100.6308</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-78.62</v>
+        <v>-0.29</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -2442,32 +2414,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101.25</v>
+        <v>100.98</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.01</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>22.6434</v>
+        <v>100.6886</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-78.61</v>
+        <v>-0.29</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -2494,32 +2466,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>100.92</v>
+        <v>100.74</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22.5988</v>
+        <v>100.4492</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-78.31999999999999</v>
+        <v>-0.29</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2538,110 +2510,6 @@
         </is>
       </c>
       <c r="L38" t="inlineStr">
-        <is>
-          <t>SEK (4.2% of the official ICE USDX basket) excluded -- no liquid CME future exists for it. The remaining five legs sum to 0.958 (not 0.96) of the official basket and are rescaled by dividing each weight by 0.958 so they re-sum to 1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>100.98</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>22.6058</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>-78.37</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Normal Trading</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SEK (4.2% of the official ICE USDX basket) excluded -- no liquid CME future exists for it. The remaining five legs sum to 0.958 (not 0.96) of the official basket and are rescaled by dividing each weight by 0.958 so they re-sum to 1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>100.74</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>22.6008</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>-78.14</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Normal Trading</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
         <is>
           <t>SEK (4.2% of the official ICE USDX basket) excluded -- no liquid CME future exists for it. The remaining five legs sum to 0.958 (not 0.96) of the official basket and are rescaled by dividing each weight by 0.958 so they re-sum to 1.0.</t>
         </is>
@@ -4638,7 +4506,7 @@
     <col width="33" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4718,15 +4586,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0065</v>
+        <v>153.7279</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-153.74</v>
+        <v>-0.01</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -4739,7 +4607,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.78</v>
+        <v>0.02</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4767,15 +4635,15 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0065</v>
+        <v>154.321</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-154.34</v>
+        <v>-0.02</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -4788,7 +4656,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4816,15 +4684,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0065</v>
+        <v>153.6098</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-153.65</v>
+        <v>-0.05</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -4837,11 +4705,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.76</v>
+        <v>0.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4865,15 +4733,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0065</v>
+        <v>153.7279</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-153.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -4886,11 +4754,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.84</v>
+        <v>0.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4914,15 +4782,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0064</v>
+        <v>156.128</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-156.21</v>
+        <v>-0.09</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -4935,11 +4803,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -4963,15 +4831,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0064</v>
+        <v>155.4847</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+2.14%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-155.56</v>
+        <v>-0.08</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -4983,12 +4851,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0.63</v>
+      <c r="J7" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -5012,15 +4880,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0063</v>
+        <v>158.8058</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-158.93</v>
+        <v>-0.13</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -5032,8 +4900,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0.4</v>
+      <c r="J8" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5061,15 +4929,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0062</v>
+        <v>160.0384</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-160.17</v>
+        <v>-0.14</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -5081,8 +4949,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0.31</v>
+      <c r="J9" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -5110,15 +4978,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0063</v>
+        <v>159.6169</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-159.76</v>
+        <v>-0.15</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -5130,8 +4998,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0.3</v>
+      <c r="J10" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -5159,15 +5027,15 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0063</v>
+        <v>159.9105</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-160.08</v>
+        <v>-0.17</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -5179,8 +5047,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>0.28</v>
+      <c r="J11" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -5208,15 +5076,15 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0063</v>
+        <v>159.223</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-159.41</v>
+        <v>-0.19</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -5228,8 +5096,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.35</v>
+      <c r="J12" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -5257,15 +5125,15 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0063</v>
+        <v>159.1596</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-159.37</v>
+        <v>-0.22</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -5277,8 +5145,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>0.41</v>
+      <c r="J13" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -5306,15 +5174,15 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0063</v>
+        <v>158.9825</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-159.22</v>
+        <v>-0.24</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -5326,8 +5194,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0.44</v>
+      <c r="J14" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -5355,15 +5223,15 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0063</v>
+        <v>158.9193</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-159.16</v>
+        <v>-0.25</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -5375,8 +5243,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0.44</v>
+      <c r="J15" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -5404,15 +5272,15 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0063</v>
+        <v>158.7554</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-159</v>
+        <v>-0.25</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -5424,8 +5292,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0.5</v>
+      <c r="J16" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -5453,15 +5321,15 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0063</v>
+        <v>158.8689</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-159.14</v>
+        <v>-0.28</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -5473,8 +5341,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>0.64</v>
+      <c r="J17" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -5502,15 +5370,15 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0063</v>
+        <v>158.0278</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-158.33</v>
+        <v>-0.31</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -5522,8 +5390,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0.59</v>
+      <c r="J18" s="4" t="n">
+        <v>0.02</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -5551,15 +5419,15 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0063</v>
+        <v>159.2737</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-159.6</v>
+        <v>-0.33</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -5572,7 +5440,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -5600,15 +5468,15 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0063</v>
+        <v>159.223</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-159.55</v>
+        <v>-0.34</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -5621,7 +5489,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.84</v>
+        <v>0.02</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -5649,15 +5517,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0063</v>
+        <v>159.0204</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-159.37</v>
+        <v>-0.35</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -5670,7 +5538,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.83</v>
+        <v>0.02</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -5698,15 +5566,15 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0063</v>
+        <v>159.1343</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-159.49</v>
+        <v>-0.36</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -5719,7 +5587,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.83</v>
+        <v>0.02</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5747,15 +5615,15 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0063</v>
+        <v>159.0963</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-159.49</v>
+        <v>-0.4</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -5768,7 +5636,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.83</v>
+        <v>0.02</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5796,15 +5664,15 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0063</v>
+        <v>158.8562</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-159.27</v>
+        <v>-0.42</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -5817,7 +5685,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5845,15 +5713,15 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0063</v>
+        <v>158.8184</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-159.22</v>
+        <v>-0.41</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -5866,7 +5734,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -5894,15 +5762,15 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0064</v>
+        <v>157.1215</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-157.53</v>
+        <v>-0.41</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -5915,7 +5783,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.79</v>
+        <v>0.02</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5943,15 +5811,15 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0063</v>
+        <v>157.8532</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-158.29</v>
+        <v>-0.44</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -5990,15 +5858,15 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0064</v>
+        <v>157.1833</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-157.65</v>
+        <v>-0.48</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -6037,15 +5905,15 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0064</v>
+        <v>157.2327</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-157.72</v>
+        <v>-0.49</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -6084,15 +5952,15 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0064</v>
+        <v>156.2866</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-156.77</v>
+        <v>-0.49</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -6131,15 +5999,15 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0063</v>
+        <v>158.3657</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-158.87</v>
+        <v>-0.51</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -6178,15 +6046,15 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0063</v>
+        <v>158.554</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-159.08</v>
+        <v>-0.53</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -6225,15 +6093,15 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0061</v>
+        <v>162.7472</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-163.32</v>
+        <v>-0.58</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -6272,15 +6140,15 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0061</v>
+        <v>163.1987</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-163.83</v>
+        <v>-0.64</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -6319,15 +6187,15 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0061</v>
+        <v>163.1188</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-163.76</v>
+        <v>-0.64</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -6366,15 +6234,15 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0061</v>
+        <v>163.1588</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-163.81</v>
+        <v>-0.66</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -6413,15 +6281,15 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0061</v>
+        <v>163.1055</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-163.78</v>
+        <v>-0.68</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -6460,15 +6328,15 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0062</v>
+        <v>162.4168</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-163.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -6507,15 +6375,15 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0062</v>
+        <v>162.4827</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-163.19</v>
+        <v>-0.71</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -6554,7 +6422,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0062</v>
+        <v>161.7861</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -6562,7 +6430,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-162.48</v>
+        <v>-0.7</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -7162,7 +7030,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3587</v>
+        <v>1.3588</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -7211,7 +7079,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3591</v>
+        <v>1.359</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -8559,7 +8427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8652,15 +8520,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7193000000000001</v>
+        <v>1.3841</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -8672,8 +8540,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0.01</v>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8701,15 +8569,15 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7213000000000001</v>
+        <v>1.3805</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -8721,8 +8589,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0.01</v>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8750,15 +8618,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7232</v>
+        <v>1.3771</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -8770,8 +8638,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0.01</v>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8799,15 +8667,15 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7244</v>
+        <v>1.3745</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -8819,8 +8687,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0.01</v>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -8848,15 +8716,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.726</v>
+        <v>1.3717</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -8868,8 +8736,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0.01</v>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8897,15 +8765,15 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7229</v>
+        <v>1.3777</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -8917,12 +8785,12 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0.01</v>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ MAJOR NEWS EVENT</t>
         </is>
       </c>
     </row>
@@ -8946,15 +8814,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7255</v>
+        <v>1.3726</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -8966,8 +8834,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>0.01</v>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8995,15 +8863,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7229</v>
+        <v>1.3774</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -9015,8 +8883,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0.01</v>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9044,15 +8912,15 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7201</v>
+        <v>1.3826</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -9064,8 +8932,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>0.01</v>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9093,15 +8961,15 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7221</v>
+        <v>1.3788</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -9113,8 +8981,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0.01</v>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -9142,15 +9010,15 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7196</v>
+        <v>1.3835</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -9162,8 +9030,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>0.01</v>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -9191,15 +9059,15 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.7222</v>
+        <v>1.3789</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -9211,8 +9079,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.01</v>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -9240,15 +9108,15 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7211</v>
+        <v>1.3809</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -9260,8 +9128,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0.01</v>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -9289,15 +9157,15 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7238</v>
+        <v>1.3759</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -9309,8 +9177,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>0.01</v>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -9325,7 +9193,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3848</v>
+        <v>1.3849</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -9338,15 +9206,15 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.7227</v>
+        <v>1.378</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -9358,8 +9226,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>0.01</v>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -9387,15 +9255,15 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7272999999999999</v>
+        <v>1.3691</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -9436,15 +9304,15 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7258</v>
+        <v>1.372</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -9485,15 +9353,15 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.7248</v>
+        <v>1.3738</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9510,7 +9378,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -9534,15 +9402,15 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.72</v>
+        <v>1.3835</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -9583,15 +9451,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7215</v>
+        <v>1.3805</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -9632,15 +9500,15 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7214</v>
+        <v>1.38</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -9681,15 +9549,15 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.7186</v>
+        <v>1.386</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -9730,15 +9598,15 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7181</v>
+        <v>1.3868</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-0.68</v>
+        <v>-0.01</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -9779,15 +9647,15 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.7194</v>
+        <v>1.3842</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-0.67</v>
+        <v>-0.01</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -9819,24 +9687,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.7181999999999999</v>
+        <v>1.3862</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.68</v>
+        <v>-0.01</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -9848,9 +9716,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -9860,15 +9726,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3938</v>
+        <v>1.4012</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -9877,15 +9743,15 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7185</v>
+        <v>1.3933</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.68</v>
+        <v>-0.01</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9897,9 +9763,7 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -9909,15 +9773,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4012</v>
+        <v>1.4007</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -9926,15 +9790,15 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.7148</v>
+        <v>1.3925</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -9956,32 +9820,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4007</v>
+        <v>1.4064</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7151</v>
+        <v>1.398</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -10003,15 +9867,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4064</v>
+        <v>1.4015</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -10020,15 +9884,15 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7122000000000001</v>
+        <v>1.3934</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -10050,32 +9914,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4042</v>
+        <v>1.3999</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7134</v>
+        <v>1.3908</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -10097,32 +9961,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4015</v>
+        <v>1.4038</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7147</v>
+        <v>1.3949</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -10144,32 +10008,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3999</v>
+        <v>1.4103</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.7157</v>
+        <v>1.4011</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-0.68</v>
+        <v>-0.01</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -10191,15 +10055,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4038</v>
+        <v>1.4124</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -10208,15 +10072,15 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7138</v>
+        <v>1.4028</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -10238,32 +10102,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4103</v>
+        <v>1.4096</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.7106</v>
+        <v>1.4001</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-0.7</v>
+        <v>-0.01</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -10285,15 +10149,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4124</v>
+        <v>1.4076</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10302,15 +10166,15 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.7096</v>
+        <v>1.3983</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-0.7</v>
+        <v>-0.01</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -10332,32 +10196,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4096</v>
+        <v>1.4084</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.711</v>
+        <v>1.3989</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-0.7</v>
+        <v>-0.01</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -10379,32 +10243,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.4076</v>
+        <v>1.4107</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7121</v>
+        <v>1.4012</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-0.7</v>
+        <v>-0.01</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -10426,32 +10290,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.4084</v>
+        <v>1.4057</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.7117</v>
+        <v>1.3964</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-0.7</v>
+        <v>-0.01</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -10465,100 +10329,6 @@
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" t="inlineStr">
-        <is>
-          <t>Normal Trading</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1.4107</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>+0.35%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.7106</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Normal Trading</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.4057</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.7131</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Backwardation (Extreme Demand)</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Normal Premium</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -10585,10 +10355,10 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10668,19 +10438,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.2248</v>
+        <v>0.8165</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -10688,8 +10458,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0.01</v>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -10717,19 +10487,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.2302</v>
+        <v>0.8129</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -10737,8 +10507,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0.01</v>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -10766,19 +10536,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.2343</v>
+        <v>0.8102</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10786,8 +10556,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0.01</v>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -10815,19 +10585,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.2369</v>
+        <v>0.8085</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10835,8 +10605,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0.01</v>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -10864,19 +10634,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.2354</v>
+        <v>0.8095</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -10884,8 +10654,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0.01</v>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -10913,19 +10683,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.2403</v>
+        <v>0.8063</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -10933,8 +10703,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0.01</v>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -10962,19 +10732,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.2312</v>
+        <v>0.8122</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10982,8 +10752,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>0.01</v>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -11011,19 +10781,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.2336</v>
+        <v>0.8106</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -11031,8 +10801,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0.01</v>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -11060,19 +10830,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2391</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11080,8 +10850,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>0.01</v>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -11109,19 +10879,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.237</v>
+        <v>0.8084</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11129,8 +10899,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0.01</v>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -11158,19 +10928,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.2455</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -11178,8 +10948,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>0.01</v>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -11207,19 +10977,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.2441</v>
+        <v>0.8038</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -11227,8 +10997,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.01</v>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -11256,19 +11026,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.2496</v>
+        <v>0.8003</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11276,8 +11046,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0.01</v>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -11305,19 +11075,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.2487</v>
+        <v>0.8008</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -11325,8 +11095,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>0.01</v>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -11354,19 +11124,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.2514</v>
+        <v>0.7991</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11374,8 +11144,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>0.01</v>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -11403,19 +11173,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.2516</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11423,8 +11193,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>0.01</v>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -11452,32 +11222,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.2565</v>
+        <v>0.7958</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+1.80%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Contango (Extreme Oversupply / Glut)</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>🎯 BANK BUY ARBITRAGE</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0.01</v>
+        <v>-0</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Normal Premium</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>⚠️ MAJOR NEWS EVENT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
@@ -11501,19 +11271,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.2343</v>
+        <v>0.8102</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11521,8 +11291,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>0.01</v>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -11550,19 +11320,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.2358</v>
+        <v>0.8092</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11570,8 +11340,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>0.01</v>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -11599,19 +11369,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.2336</v>
+        <v>0.8106</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -11619,8 +11389,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0.01</v>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -11648,19 +11418,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.2325</v>
+        <v>0.8114</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11668,8 +11438,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>0.01</v>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -11697,19 +11467,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.2333</v>
+        <v>0.8109</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11717,8 +11487,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0.01</v>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -11746,19 +11516,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.2371</v>
+        <v>0.8083</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11766,8 +11536,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>0.01</v>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -11795,19 +11565,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.2388</v>
+        <v>0.8072</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -11815,8 +11585,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>0.01</v>
+      <c r="J25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -11844,19 +11614,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.2433</v>
+        <v>0.8043</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11864,8 +11634,8 @@
           <t>Normal Premium</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>0.01</v>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -11893,19 +11663,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.2364</v>
+        <v>0.8088</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -11940,19 +11710,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.2445</v>
+        <v>0.8035</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -11987,19 +11757,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.2411</v>
+        <v>0.8057</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -12034,19 +11804,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.24</v>
+        <v>0.8064</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12081,19 +11851,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.2434</v>
+        <v>0.8042</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -12128,19 +11898,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.2492</v>
+        <v>0.8005</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -12175,19 +11945,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.2337</v>
+        <v>0.8105</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -12222,19 +11992,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.2275</v>
+        <v>0.8147</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12269,19 +12039,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.2275</v>
+        <v>0.8147</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -12316,19 +12086,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.229</v>
+        <v>0.8137</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -12363,19 +12133,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.2309</v>
+        <v>0.8124</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -12410,19 +12180,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.2349</v>
+        <v>0.8098</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -12457,19 +12227,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.2376</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -12504,7 +12274,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.2421</v>
+        <v>0.8051</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -12512,11 +12282,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Contango (Normal Market)</t>
+        <v>-0</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Backwardation (Extreme Demand)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">

--- a/DXY_Price_Gap_Theory_2026.xlsx
+++ b/DXY_Price_Gap_Theory_2026.xlsx
@@ -2785,7 +2785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2867,28 +2867,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.1556</v>
+        <v>1.1478</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.1599</v>
+        <v>1.1521</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2921,28 +2921,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.1593</v>
+        <v>1.1541</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.1595</v>
+        <v>1.1584</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>+0.370%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -2958,9 +2958,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Carry Richening (Elevated)</t>
         </is>
       </c>
       <c r="K3" s="6" t="n">
@@ -2968,35 +2968,35 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.161</v>
+        <v>1.1556</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.1612</v>
+        <v>1.1599</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>+0.370%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3012,9 +3012,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Carry Richening (Elevated)</t>
         </is>
       </c>
       <c r="K4" s="6" t="n">
@@ -3022,35 +3022,35 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1626</v>
+        <v>1.1593</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.1629</v>
+        <v>1.1595</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>+0.020%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3083,28 +3083,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.1629</v>
+        <v>1.161</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.1632</v>
+        <v>1.1612</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>+0.030%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3137,15 +3137,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1611</v>
+        <v>1.1626</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.1616</v>
+        <v>1.1629</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>+0.040%</t>
+          <t>+0.020%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3191,28 +3191,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1.1629</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1.1632</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1.1636</v>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3245,15 +3245,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.1585</v>
+        <v>1.1611</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3262,11 +3262,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.1591</v>
+        <v>1.1616</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>+0.060%</t>
+          <t>+0.040%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3299,15 +3299,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.1591</v>
+        <v>1.1632</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3316,11 +3316,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.1597</v>
+        <v>1.1636</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>+0.060%</t>
+          <t>+0.030%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3353,15 +3353,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1616</v>
+        <v>1.1585</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3370,11 +3370,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.1623</v>
+        <v>1.1591</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3407,28 +3407,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.158</v>
+        <v>1.1591</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.1588</v>
+        <v>1.1597</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>+0.070%</t>
+          <t>+0.060%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3461,15 +3461,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1648</v>
+        <v>1.1616</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3478,11 +3478,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.1657</v>
+        <v>1.1623</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>+0.070%</t>
+          <t>+0.060%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3515,28 +3515,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.165</v>
+        <v>1.158</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.166</v>
+        <v>1.1588</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>+0.080%</t>
+          <t>+0.070%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3569,15 +3569,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1674</v>
+        <v>1.1648</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3586,11 +3586,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.1684</v>
+        <v>1.1657</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>+0.090%</t>
+          <t>+0.070%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -3623,15 +3623,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1662</v>
+        <v>1.165</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3640,11 +3640,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.1673</v>
+        <v>1.166</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>+0.100%</t>
+          <t>+0.080%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3677,28 +3677,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.168</v>
+        <v>1.1674</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.1691</v>
+        <v>1.1684</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>+0.100%</t>
+          <t>+0.090%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3731,28 +3731,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>1.1662</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>1.1673</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.1684</v>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3785,28 +3785,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.167</v>
+        <v>1.168</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.1683</v>
+        <v>1.1691</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>+0.110%</t>
+          <t>+0.100%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3839,36 +3839,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1574</v>
+        <v>1.1673</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>+0.01%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1.1588</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>+0.120%</t>
+          <t>+0.100%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3893,15 +3893,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1573</v>
+        <v>1.167</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3910,11 +3910,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.1587</v>
+        <v>1.1683</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>+0.120%</t>
+          <t>+0.110%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3947,28 +3947,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1564</v>
+        <v>1.1574</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.1579</v>
+        <v>1.1588</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4001,46 +4001,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1529</v>
+        <v>1.1573</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.1587</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>+0.07%</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1.1544</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>+0.130%</t>
+          <t>+0.120%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &gt; Spot</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K23" s="6" t="n">
@@ -4055,15 +4055,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.152</v>
+        <v>1.1564</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4072,11 +4072,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.1537</v>
+        <v>1.1579</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>+0.140%</t>
+          <t>+0.120%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &gt; Spot</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K24" s="6" t="n">
@@ -4109,15 +4109,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1539</v>
+        <v>1.1529</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4126,11 +4126,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.1557</v>
+        <v>1.1544</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>+0.150%</t>
+          <t>+0.130%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -4163,15 +4163,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.154</v>
+        <v>1.152</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4180,11 +4180,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.1557</v>
+        <v>1.1537</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>+0.150%</t>
+          <t>+0.140%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4217,28 +4217,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1565</v>
+        <v>1.1539</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.1582</v>
+        <v>1.1557</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4271,15 +4271,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1524</v>
+        <v>1.154</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4288,11 +4288,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.1543</v>
+        <v>1.1557</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>+0.160%</t>
+          <t>+0.150%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4313,7 +4313,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -4323,15 +4325,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1553</v>
+        <v>1.1565</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4340,11 +4342,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.1572</v>
+        <v>1.1582</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4352,7 +4354,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>+0.170%</t>
+          <t>+0.150%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -4365,7 +4367,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -4375,15 +4379,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.153</v>
+        <v>1.1524</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4392,11 +4396,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.1551</v>
+        <v>1.1543</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>+0.170%</t>
+          <t>+0.160%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4427,28 +4431,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1514</v>
+        <v>1.1553</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.1533</v>
+        <v>1.1572</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4479,15 +4483,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1533</v>
+        <v>1.153</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4496,11 +4500,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.1553</v>
+        <v>1.1551</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4508,7 +4512,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>+0.180%</t>
+          <t>+0.170%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4531,28 +4535,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>1.1514</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>1.1533</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>+0.75%</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1.1554</v>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4560,7 +4564,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>+0.180%</t>
+          <t>+0.170%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4583,15 +4587,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1448</v>
+        <v>1.1533</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4600,11 +4604,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.1471</v>
+        <v>1.1553</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4612,7 +4616,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>+0.200%</t>
+          <t>+0.180%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4635,15 +4639,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1388</v>
+        <v>1.1533</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4652,11 +4656,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.1411</v>
+        <v>1.1554</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4664,7 +4668,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>+0.210%</t>
+          <t>+0.180%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4687,28 +4691,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1367</v>
+        <v>1.1448</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.1392</v>
+        <v>1.1471</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4716,7 +4720,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>+0.220%</t>
+          <t>+0.200%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4739,28 +4743,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.1369</v>
+        <v>1.1388</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.1394</v>
+        <v>1.1411</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4768,7 +4772,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>+0.220%</t>
+          <t>+0.210%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4791,28 +4795,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1376</v>
+        <v>1.1367</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.1401</v>
+        <v>1.1392</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4820,7 +4824,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>+0.230%</t>
+          <t>+0.220%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4843,15 +4847,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1411</v>
+        <v>1.1369</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4860,11 +4864,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.1437</v>
+        <v>1.1394</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4872,7 +4876,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>+0.230%</t>
+          <t>+0.220%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -4895,28 +4899,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>1.1376</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>1.1401</v>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1.1428</v>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4947,28 +4951,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1415</v>
+        <v>1.1411</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.1442</v>
+        <v>1.1437</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4976,7 +4980,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>+0.240%</t>
+          <t>+0.230%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -4991,6 +4995,110 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.1401</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1.1428</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>+0.230%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.1415</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1.1442</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>+0.240%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -5007,7 +5115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5089,28 +5197,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>154.081</v>
+        <v>155.812</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>152.9754</v>
+        <v>154.703</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5118,7 +5226,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-0.720%</t>
+          <t>-0.710%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -5132,7 +5240,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -5143,36 +5251,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153.742</v>
+        <v>155.091</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>153.7279</v>
+        <v>153.9764</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0.01</v>
+        <v>-1.11</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-0.010%</t>
+          <t>-0.720%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -5180,53 +5288,53 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>154.343</v>
+        <v>154.081</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>154.321</v>
+        <v>152.9754</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.02</v>
+        <v>-1.11</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0.010%</t>
+          <t>-0.720%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5234,53 +5342,53 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>153.659</v>
+        <v>153.742</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+0.14</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>153.6098</v>
+        <v>153.7279</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0.030%</t>
+          <t>-0.010%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5305,36 +5413,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>153.799</v>
+        <v>154.343</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>153.7279</v>
+        <v>154.321</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0.050%</t>
+          <t>-0.010%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5359,36 +5467,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156.217</v>
+        <v>153.659</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+0.21</t>
+          <t>+0.14</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>156.128</v>
+        <v>153.6098</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0.060%</t>
+          <t>-0.030%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5413,32 +5521,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155.566</v>
+        <v>153.799</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>155.4847</v>
+        <v>153.7279</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -5467,36 +5575,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158.932</v>
+        <v>156.217</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>158.8058</v>
+        <v>156.128</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0.080%</t>
+          <t>-0.060%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5521,36 +5629,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160.176</v>
+        <v>155.566</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>160.0384</v>
+        <v>155.4847</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0.090%</t>
+          <t>-0.050%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5575,36 +5683,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159.767</v>
+        <v>158.932</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>159.6169</v>
+        <v>158.8058</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0.090%</t>
+          <t>-0.080%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5629,36 +5737,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>160.083</v>
+        <v>160.176</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>159.9105</v>
+        <v>160.0384</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0.110%</t>
+          <t>-0.090%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5683,36 +5791,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>159.413</v>
+        <v>159.767</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>159.223</v>
+        <v>159.6169</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0.120%</t>
+          <t>-0.090%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5737,36 +5845,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>159.38</v>
+        <v>160.083</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>159.1596</v>
+        <v>159.9105</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-0.22</v>
+        <v>-0.17</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0.140%</t>
+          <t>-0.110%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5791,36 +5899,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159.226</v>
+        <v>159.413</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>159.223</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>+0.04%</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>158.9825</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
       <c r="G15" t="n">
-        <v>-0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0.150%</t>
+          <t>-0.120%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5845,11 +5953,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>159.167</v>
+        <v>159.38</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -5858,23 +5966,23 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>158.9193</v>
+        <v>159.1596</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0.160%</t>
+          <t>-0.140%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5899,15 +6007,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>159.009</v>
+        <v>159.226</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -5916,19 +6024,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>158.7554</v>
+        <v>158.9825</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0.160%</t>
+          <t>-0.150%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5953,36 +6061,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159.148</v>
+        <v>159.167</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>158.8689</v>
+        <v>158.9193</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0.180%</t>
+          <t>-0.160%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6007,36 +6115,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>158.333</v>
+        <v>159.009</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>158.0278</v>
+        <v>158.7554</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-0.31</v>
+        <v>-0.25</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0.190%</t>
+          <t>-0.160%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -6061,36 +6169,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>159.602</v>
+        <v>159.148</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>159.2737</v>
+        <v>158.8689</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-0.33</v>
+        <v>-0.28</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0.210%</t>
+          <t>-0.180%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6115,36 +6223,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>159.56</v>
+        <v>158.333</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>159.223</v>
+        <v>158.0278</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0.210%</t>
+          <t>-0.190%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6169,36 +6277,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>159.373</v>
+        <v>159.602</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>159.0204</v>
+        <v>159.2737</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-0.35</v>
+        <v>-0.33</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0.220%</t>
+          <t>-0.210%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6223,46 +6331,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>159.499</v>
+        <v>159.56</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>159.1343</v>
+        <v>159.223</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0.230%</t>
+          <t>-0.210%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K23" s="4" t="n">
@@ -6277,46 +6385,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>159.498</v>
+        <v>159.373</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>159.0963</v>
+        <v>159.0204</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0.250%</t>
+          <t>-0.220%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K24" s="4" t="n">
@@ -6331,24 +6439,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>159.275</v>
+        <v>159.499</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>158.8562</v>
+        <v>159.1343</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -6356,11 +6464,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0.260%</t>
+          <t>-0.230%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6385,36 +6493,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>159.231</v>
+        <v>159.498</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>158.8184</v>
+        <v>159.0963</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0.260%</t>
+          <t>-0.250%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6439,32 +6547,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>157.533</v>
+        <v>159.275</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>157.1215</v>
+        <v>158.8562</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -6493,36 +6601,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>158.292</v>
+        <v>159.231</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>157.8532</v>
+        <v>158.8184</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0.280%</t>
+          <t>-0.260%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6535,7 +6643,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -6545,36 +6655,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>157.661</v>
+        <v>157.533</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>157.1833</v>
+        <v>157.1215</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.48</v>
+        <v>-0.41</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>-0.260%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6587,7 +6697,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="4" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -6597,36 +6709,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>157.725</v>
+        <v>158.292</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+0.38</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>157.2327</v>
+        <v>157.8532</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0.310%</t>
+          <t>-0.280%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -6649,36 +6761,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>156.772</v>
+        <v>157.661</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>156.2866</v>
+        <v>157.1833</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0.310%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -6701,36 +6813,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>158.878</v>
+        <v>157.725</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+0.41</t>
+          <t>+0.38</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>158.3657</v>
+        <v>157.2327</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0.320%</t>
+          <t>-0.310%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6753,36 +6865,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>159.087</v>
+        <v>156.772</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>158.554</v>
+        <v>156.2866</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0.340%</t>
+          <t>-0.310%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -6805,36 +6917,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>163.329</v>
+        <v>158.878</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+0.41</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>162.7472</v>
+        <v>158.3657</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-0.58</v>
+        <v>-0.51</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0.360%</t>
+          <t>-0.320%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6857,36 +6969,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>163.835</v>
+        <v>159.087</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>163.1987</v>
+        <v>158.554</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-0.64</v>
+        <v>-0.53</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-0.390%</t>
+          <t>-0.340%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -6909,36 +7021,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>163.763</v>
+        <v>163.329</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>163.1188</v>
+        <v>162.7472</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-0.64</v>
+        <v>-0.58</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0.390%</t>
+          <t>-0.360%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -6961,36 +7073,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>163.814</v>
+        <v>163.835</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>163.1588</v>
+        <v>163.1987</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0.400%</t>
+          <t>-0.390%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -7013,36 +7125,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>163.786</v>
+        <v>163.763</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+0.01</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>163.1055</v>
+        <v>163.1188</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-0.68</v>
+        <v>-0.64</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0.420%</t>
+          <t>-0.390%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -7065,36 +7177,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>163.109</v>
+        <v>163.814</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>162.4168</v>
+        <v>163.1588</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-0.420%</t>
+          <t>-0.400%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -7117,36 +7229,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>163.194</v>
+        <v>163.786</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>+0.01</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>162.4827</v>
+        <v>163.1055</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>-0.440%</t>
+          <t>-0.420%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -7169,36 +7281,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>162.485</v>
+        <v>163.109</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>161.7861</v>
+        <v>162.4168</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-0.430%</t>
+          <t>-0.420%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -7213,6 +7325,110 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>163.194</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>162.4827</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-0.440%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>162.485</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>161.7861</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-0.430%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -7229,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7311,15 +7527,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351</v>
+        <v>1.3388</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7328,11 +7544,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.3514</v>
+        <v>1.3394</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7340,7 +7556,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>+0.030%</t>
+          <t>+0.050%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -7365,15 +7581,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.3524</v>
+        <v>1.3476</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -7382,11 +7598,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.3526</v>
+        <v>1.348</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -7394,7 +7610,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>+0.030%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -7402,9 +7618,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Carry Richening (Elevated)</t>
         </is>
       </c>
       <c r="K3" s="6" t="n">
@@ -7412,22 +7628,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.3509</v>
+        <v>1.351</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7436,11 +7652,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.3511</v>
+        <v>1.3514</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -7448,7 +7664,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>+0.030%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -7456,9 +7672,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Carry Richening (Elevated)</t>
         </is>
       </c>
       <c r="K4" s="6" t="n">
@@ -7466,22 +7682,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.3542</v>
+        <v>1.3524</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -7490,11 +7706,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.3542</v>
+        <v>1.3526</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -7502,7 +7718,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7510,9 +7726,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K5" s="6" t="n">
@@ -7527,28 +7743,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3546</v>
+        <v>1.3509</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3547</v>
+        <v>1.3511</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -7581,15 +7797,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3514</v>
+        <v>1.3542</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7598,19 +7814,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.3514</v>
+        <v>1.3542</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7618,9 +7834,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Carry Cheapening (Elevated)</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K7" s="6" t="n">
@@ -7628,35 +7844,35 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>⚠️ CARRY REGIME SHIFT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3537</v>
+        <v>1.3546</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.3538</v>
+        <v>1.3547</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -7672,9 +7888,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K8" s="6" t="n">
@@ -7689,15 +7905,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3484</v>
+        <v>1.3514</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7706,19 +7922,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.3485</v>
+        <v>1.3514</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>-0.000%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7726,9 +7942,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K9" s="6" t="n">
@@ -7736,22 +7952,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3514</v>
+        <v>1.3537</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7760,11 +7976,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3515</v>
+        <v>1.3538</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -7780,9 +7996,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K10" s="6" t="n">
@@ -7797,15 +8013,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3547</v>
+        <v>1.3484</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -7814,11 +8030,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3548</v>
+        <v>1.3485</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -7851,15 +8067,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3531</v>
+        <v>1.3514</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7868,11 +8084,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3532</v>
+        <v>1.3515</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -7888,9 +8104,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K12" s="6" t="n">
@@ -7905,15 +8121,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3587</v>
+        <v>1.3547</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -7922,11 +8138,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3588</v>
+        <v>1.3548</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -7934,7 +8150,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7959,28 +8175,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3591</v>
+        <v>1.3531</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3591</v>
+        <v>1.3532</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -7988,7 +8204,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8013,28 +8229,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3644</v>
+        <v>1.3587</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.3645</v>
+        <v>1.3588</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -8042,7 +8258,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -8050,9 +8266,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K15" s="6" t="n">
@@ -8067,28 +8283,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3628</v>
+        <v>1.3591</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3629</v>
+        <v>1.3591</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -8096,7 +8312,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8121,28 +8337,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3649</v>
+        <v>1.3644</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.3649</v>
+        <v>1.3645</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -8150,7 +8366,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8160,7 +8376,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Carry Drifting (Narrower)</t>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K17" s="6" t="n">
@@ -8175,15 +8391,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3625</v>
+        <v>1.3628</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -8192,11 +8408,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.3626</v>
+        <v>1.3629</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -8229,15 +8445,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3603</v>
+        <v>1.3649</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -8246,11 +8462,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.3604</v>
+        <v>1.3649</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -8258,7 +8474,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8266,9 +8482,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K19" s="6" t="n">
@@ -8283,28 +8499,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3533</v>
+        <v>1.3625</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.3534</v>
+        <v>1.3626</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -8337,28 +8553,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3537</v>
+        <v>1.3603</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.3537</v>
+        <v>1.3604</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -8366,7 +8582,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -8391,28 +8607,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3532</v>
+        <v>1.3533</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.3532</v>
+        <v>1.3534</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -8420,7 +8636,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8428,9 +8644,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K22" s="6" t="n">
@@ -8445,15 +8661,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3484</v>
+        <v>1.3537</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -8462,11 +8678,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.3484</v>
+        <v>1.3537</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -8479,7 +8695,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
+          <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8499,28 +8715,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3487</v>
+        <v>1.3532</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.3488</v>
+        <v>1.3532</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -8528,17 +8744,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &gt; Spot</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K24" s="6" t="n">
@@ -8553,11 +8769,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3502</v>
+        <v>1.3484</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -8566,15 +8782,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.3502</v>
+        <v>1.3484</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -8607,28 +8823,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3506</v>
+        <v>1.3487</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.3507</v>
+        <v>1.3488</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -8661,15 +8877,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3499</v>
+        <v>1.3502</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -8678,11 +8894,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.3501</v>
+        <v>1.3502</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -8690,7 +8906,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8715,15 +8931,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3458</v>
+        <v>1.3506</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -8732,11 +8948,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.3458</v>
+        <v>1.3507</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -8744,7 +8960,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -8757,7 +8973,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -8767,15 +8985,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3469</v>
+        <v>1.3499</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -8784,11 +9002,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.3469</v>
+        <v>1.3501</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -8796,7 +9014,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -8809,7 +9027,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -8819,15 +9039,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.345</v>
+        <v>1.3458</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8836,11 +9056,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.3451</v>
+        <v>1.3458</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -8848,7 +9068,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -8871,28 +9091,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3433</v>
+        <v>1.3469</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.3433</v>
+        <v>1.3469</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -8923,15 +9143,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3485</v>
+        <v>1.345</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8940,11 +9160,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.3486</v>
+        <v>1.3451</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -8975,15 +9195,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3474</v>
+        <v>1.3433</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8992,11 +9212,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.3475</v>
+        <v>1.3433</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -9004,7 +9224,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -9027,15 +9247,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3361</v>
+        <v>1.3485</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9044,11 +9264,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.3362</v>
+        <v>1.3486</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -9079,15 +9299,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.329</v>
+        <v>1.3474</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9096,11 +9316,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.3291</v>
+        <v>1.3475</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -9131,28 +9351,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3288</v>
+        <v>1.3361</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.3289</v>
+        <v>1.3362</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -9183,28 +9403,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3326</v>
+        <v>1.329</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.3327</v>
+        <v>1.3291</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -9235,28 +9455,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3314</v>
+        <v>1.3288</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.3316</v>
+        <v>1.3289</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -9287,15 +9507,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3372</v>
+        <v>1.3326</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -9304,11 +9524,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.3374</v>
+        <v>1.3327</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9339,15 +9559,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.3379</v>
+        <v>1.3314</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -9356,11 +9576,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.338</v>
+        <v>1.3316</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9391,28 +9611,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3433</v>
+        <v>1.3372</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.3434</v>
+        <v>1.3374</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9420,7 +9640,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9435,6 +9655,110 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.3379</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>-0.40%</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>+0.010%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.3433</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1.3434</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -11565,7 +11889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11647,15 +11971,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8162</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -11664,11 +11988,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8078</v>
+        <v>0.8158</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -11676,7 +12000,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-1.030%</t>
+          <t>-1.020%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -11701,36 +12025,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8167</v>
+        <v>0.8184</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8165</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-0.020%</t>
+          <t>-1.020%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -11738,9 +12062,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K3" s="6" t="n">
@@ -11748,22 +12072,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8129</v>
+        <v>0.8162</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -11772,19 +12096,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8129</v>
+        <v>0.8078</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.07%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0.010%</t>
+          <t>-1.030%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -11792,9 +12116,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K4" s="6" t="n">
@@ -11802,22 +12126,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8105</v>
+        <v>0.8167</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -11826,11 +12150,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8102</v>
+        <v>0.8165</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -11838,7 +12162,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0.040%</t>
+          <t>-0.020%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -11863,15 +12187,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8089</v>
+        <v>0.8129</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -11880,11 +12204,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8085</v>
+        <v>0.8129</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -11892,7 +12216,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0.050%</t>
+          <t>-0.010%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11917,15 +12241,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -11934,11 +12258,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8095</v>
+        <v>0.8102</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -11946,7 +12270,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0.070%</t>
+          <t>-0.040%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11971,15 +12295,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8068</v>
+        <v>0.8089</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -11988,11 +12312,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8063</v>
+        <v>0.8085</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -12000,7 +12324,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0.070%</t>
+          <t>-0.050%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -12025,15 +12349,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8131</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -12042,11 +12366,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8122</v>
+        <v>0.8095</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -12054,7 +12378,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0.110%</t>
+          <t>-0.070%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -12079,15 +12403,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8116</v>
+        <v>0.8068</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -12096,11 +12420,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8106</v>
+        <v>0.8063</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -12108,7 +12432,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0.130%</t>
+          <t>-0.070%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -12133,15 +12457,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8082</v>
+        <v>0.8131</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -12150,11 +12474,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8122</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -12162,7 +12486,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0.140%</t>
+          <t>-0.110%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -12187,15 +12511,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8096</v>
+        <v>0.8116</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -12204,11 +12528,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8084</v>
+        <v>0.8106</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -12216,7 +12540,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0.150%</t>
+          <t>-0.130%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -12241,15 +12565,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8042</v>
+        <v>0.8082</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -12258,11 +12582,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -12270,7 +12594,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0.160%</t>
+          <t>-0.140%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -12295,15 +12619,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8053</v>
+        <v>0.8096</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -12312,11 +12636,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8038</v>
+        <v>0.8084</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -12324,7 +12648,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0.190%</t>
+          <t>-0.150%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12349,15 +12673,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8042</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -12366,11 +12690,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8003</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -12378,7 +12702,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-0.160%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -12403,28 +12727,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8025</v>
+        <v>0.8053</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8008</v>
+        <v>0.8038</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -12432,7 +12756,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0.210%</t>
+          <t>-0.190%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12457,15 +12781,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -12474,11 +12798,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7991</v>
+        <v>0.8003</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -12486,7 +12810,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0.220%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12511,28 +12835,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.8008</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>+0.35%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.7989000000000001</v>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -12540,7 +12864,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0.230%</t>
+          <t>-0.210%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -12565,15 +12889,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.798</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -12582,11 +12906,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.7958</v>
+        <v>0.7991</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1.77%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -12594,7 +12918,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0.270%</t>
+          <t>-0.220%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -12619,15 +12943,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8125</v>
+        <v>0.8008</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12636,11 +12960,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8102</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -12648,7 +12972,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0.280%</t>
+          <t>-0.230%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12673,15 +12997,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8115</v>
+        <v>0.798</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -12690,11 +13014,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8092</v>
+        <v>0.7958</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -12702,7 +13026,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0.280%</t>
+          <t>-0.270%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -12727,15 +13051,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -12744,11 +13068,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8106</v>
+        <v>0.8102</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -12756,7 +13080,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>-0.280%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12781,15 +13105,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8139</v>
+        <v>0.8115</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -12798,11 +13122,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8114</v>
+        <v>0.8092</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -12810,17 +13134,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0.310%</t>
+          <t>-0.280%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K23" s="6" t="n">
@@ -12835,15 +13159,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8136</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -12852,11 +13176,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8109</v>
+        <v>0.8106</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -12864,17 +13188,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0.340%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K24" s="6" t="n">
@@ -12889,15 +13213,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8112</v>
+        <v>0.8139</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -12906,11 +13230,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8083</v>
+        <v>0.8114</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -12918,7 +13242,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0.360%</t>
+          <t>-0.310%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12943,15 +13267,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8102</v>
+        <v>0.8136</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -12960,11 +13284,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8072</v>
+        <v>0.8109</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -12972,7 +13296,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0.370%</t>
+          <t>-0.340%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12997,15 +13321,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8073</v>
+        <v>0.8112</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -13014,11 +13338,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8043</v>
+        <v>0.8083</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -13026,7 +13350,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0.370%</t>
+          <t>-0.360%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -13051,28 +13375,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8119</v>
+        <v>0.8102</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8088</v>
+        <v>0.8072</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -13080,7 +13404,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0.380%</t>
+          <t>-0.370%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13093,7 +13417,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -13103,15 +13429,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8068</v>
+        <v>0.8073</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -13120,11 +13446,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8035</v>
+        <v>0.8043</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -13132,7 +13458,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0.410%</t>
+          <t>-0.370%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13145,7 +13471,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -13155,28 +13483,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8092</v>
+        <v>0.8119</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8057</v>
+        <v>0.8088</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -13184,7 +13512,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0.430%</t>
+          <t>-0.380%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -13207,15 +13535,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8099</v>
+        <v>0.8068</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -13224,11 +13552,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8064</v>
+        <v>0.8035</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -13236,7 +13564,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0.430%</t>
+          <t>-0.410%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -13259,28 +13587,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8079</v>
+        <v>0.8092</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8042</v>
+        <v>0.8057</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -13288,7 +13616,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0.450%</t>
+          <t>-0.430%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -13311,15 +13639,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8042</v>
+        <v>0.8099</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -13328,11 +13656,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.8005</v>
+        <v>0.8064</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -13340,7 +13668,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0.460%</t>
+          <t>-0.430%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -13363,28 +13691,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8145</v>
+        <v>0.8079</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8105</v>
+        <v>0.8042</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -13392,7 +13720,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0.490%</t>
+          <t>-0.450%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -13415,15 +13743,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8189</v>
+        <v>0.8042</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -13432,11 +13760,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8147</v>
+        <v>0.8005</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -13444,7 +13772,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-0.510%</t>
+          <t>-0.460%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -13467,15 +13795,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.819</v>
+        <v>0.8145</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -13484,11 +13812,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8147</v>
+        <v>0.8105</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -13496,7 +13824,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0.530%</t>
+          <t>-0.490%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -13519,15 +13847,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8181</v>
+        <v>0.8189</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -13536,11 +13864,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.8137</v>
+        <v>0.8147</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -13548,7 +13876,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0.530%</t>
+          <t>-0.510%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -13571,15 +13899,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8169</v>
+        <v>0.819</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -13588,11 +13916,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.8124</v>
+        <v>0.8147</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -13600,7 +13928,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0.550%</t>
+          <t>-0.530%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -13623,15 +13951,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8145</v>
+        <v>0.8181</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -13640,11 +13968,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8098</v>
+        <v>0.8137</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -13652,7 +13980,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-0.570%</t>
+          <t>-0.530%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -13675,15 +14003,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8128</v>
+        <v>0.8169</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -13692,11 +14020,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8124</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -13704,7 +14032,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>-0.590%</t>
+          <t>-0.550%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -13727,28 +14055,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8099</v>
+        <v>0.8145</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.8051</v>
+        <v>0.8098</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -13756,7 +14084,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-0.590%</t>
+          <t>-0.570%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -13771,6 +14099,110 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.8128</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-0.590%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-0.590%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>

--- a/DXY_Price_Gap_Theory_2026.xlsx
+++ b/DXY_Price_Gap_Theory_2026.xlsx
@@ -7154,7 +7154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7236,36 +7236,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158.196</v>
+        <v>158.666</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>157.4183</v>
+        <v>157.8781</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-0.490%</t>
+          <t>-0.500%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -7290,28 +7290,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>157.84</v>
+        <v>158.196</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>+0.03</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>157.0598</v>
+        <v>157.4183</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -7327,9 +7327,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
@@ -7344,36 +7344,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157.946</v>
+        <v>157.84</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>+0.09</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>157.1092</v>
+        <v>157.0598</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.84</v>
+        <v>-0.78</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0.530%</t>
+          <t>-0.490%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -7398,36 +7398,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>158.122</v>
+        <v>157.946</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>157.2574</v>
+        <v>157.1092</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.86</v>
+        <v>-0.84</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0.550%</t>
+          <t>-0.530%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7452,15 +7452,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>158.005</v>
+        <v>158.122</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7469,15 +7469,15 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>157.1339</v>
+        <v>157.2574</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7506,28 +7506,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157.786</v>
+        <v>158.005</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>156.912</v>
+        <v>157.1339</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -7560,36 +7560,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>158.069</v>
+        <v>157.786</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>157.1833</v>
+        <v>156.912</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-0.89</v>
+        <v>-0.87</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0.560%</t>
+          <t>-0.550%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7602,8 +7602,8 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1</v>
+      <c r="K8" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -7614,36 +7614,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157.342</v>
+        <v>158.069</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>156.4211</v>
+        <v>157.1833</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-0.92</v>
+        <v>-0.89</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0.590%</t>
+          <t>-0.560%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7668,36 +7668,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157.188</v>
+        <v>157.342</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>+0.11</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>156.25</v>
+        <v>156.4211</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>-0.590%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7722,36 +7722,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157.389</v>
+        <v>157.188</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>156.4211</v>
+        <v>156.25</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-0.97</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0.610%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7776,28 +7776,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>157.172</v>
+        <v>157.389</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156.2012</v>
+        <v>156.4211</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0.620%</t>
+          <t>-0.610%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7830,36 +7830,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>158.866</v>
+        <v>157.172</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-1.07%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>157.8657</v>
+        <v>156.2012</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0.630%</t>
+          <t>-0.620%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7884,36 +7884,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>158.282</v>
+        <v>158.866</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>157.2327</v>
+        <v>157.8657</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0.660%</t>
+          <t>-0.630%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7921,9 +7921,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K14" s="3" t="n">
@@ -7938,36 +7938,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>157.497</v>
+        <v>158.282</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156.47</v>
+        <v>157.2327</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-1.03</v>
+        <v>-1.05</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0.650%</t>
+          <t>-0.660%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7992,28 +7992,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>157.459</v>
+        <v>157.497</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>156.4333</v>
+        <v>156.47</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -8046,32 +8046,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>156.687</v>
+        <v>157.459</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>+0.11</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>155.6663</v>
+        <v>156.4333</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-1.02</v>
+        <v>-1.03</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8100,36 +8100,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>156.017</v>
+        <v>156.687</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+0.40</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>154.9787</v>
+        <v>155.6663</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0.670%</t>
+          <t>-0.650%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8154,36 +8154,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>155.812</v>
+        <v>156.017</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>+0.40</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>154.703</v>
+        <v>154.9787</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-1.11</v>
+        <v>-1.04</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0.710%</t>
+          <t>-0.670%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8191,45 +8191,45 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Carry Cheapening (Elevated)</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>⚠️ CARRY REGIME SHIFT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>155.091</v>
+        <v>155.812</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+0.21</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>153.9764</v>
+        <v>154.703</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0.720%</t>
+          <t>-0.710%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -8262,28 +8262,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>154.081</v>
+        <v>155.091</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>152.9754</v>
+        <v>153.9764</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -8316,36 +8316,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.742</v>
+        <v>154.081</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>153.7279</v>
+        <v>152.9754</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-0.01</v>
+        <v>-1.11</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0.010%</t>
+          <t>-0.720%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8353,49 +8353,49 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0.02</v>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>154.343</v>
+        <v>153.742</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>154.321</v>
+        <v>153.7279</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8424,36 +8424,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>153.659</v>
+        <v>154.343</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>153.6098</v>
+        <v>154.321</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0.030%</t>
+          <t>-0.010%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8478,36 +8478,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>153.799</v>
+        <v>153.659</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>+0.14</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>153.7279</v>
+        <v>153.6098</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0.050%</t>
+          <t>-0.030%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -8532,36 +8532,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>156.217</v>
+        <v>153.799</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+0.21</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>156.128</v>
+        <v>153.7279</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0.060%</t>
+          <t>-0.050%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -8586,36 +8586,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>155.566</v>
+        <v>156.217</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>155.4847</v>
+        <v>156.128</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0.050%</t>
+          <t>-0.060%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8640,36 +8640,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>158.932</v>
+        <v>155.566</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>158.8058</v>
+        <v>155.4847</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0.080%</t>
+          <t>-0.050%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -8694,36 +8694,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>160.176</v>
+        <v>158.932</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>160.0384</v>
+        <v>158.8058</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0.090%</t>
+          <t>-0.080%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -8748,32 +8748,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>159.767</v>
+        <v>160.176</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>159.6169</v>
+        <v>160.0384</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -8802,36 +8802,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>160.083</v>
+        <v>159.767</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>159.9105</v>
+        <v>159.6169</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0.110%</t>
+          <t>-0.090%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8856,36 +8856,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>159.413</v>
+        <v>160.083</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>159.223</v>
+        <v>159.9105</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0.120%</t>
+          <t>-0.110%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8910,36 +8910,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>159.38</v>
+        <v>159.413</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>159.1596</v>
+        <v>159.223</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0.140%</t>
+          <t>-0.120%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -8964,36 +8964,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>159.226</v>
+        <v>159.38</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>158.9825</v>
+        <v>159.1596</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0.150%</t>
+          <t>-0.140%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -9018,36 +9018,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>159.167</v>
+        <v>159.226</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>158.9193</v>
+        <v>158.9825</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-0.160%</t>
+          <t>-0.150%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -9072,28 +9072,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>159.009</v>
+        <v>159.167</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>158.7554</v>
+        <v>158.9193</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -9126,36 +9126,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>159.148</v>
+        <v>159.009</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>158.8689</v>
+        <v>158.7554</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0.180%</t>
+          <t>-0.160%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -9180,36 +9180,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>158.333</v>
+        <v>159.148</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>158.0278</v>
+        <v>158.8689</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-0.31</v>
+        <v>-0.28</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0.190%</t>
+          <t>-0.180%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -9234,36 +9234,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>159.602</v>
+        <v>158.333</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>159.2737</v>
+        <v>158.0278</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-0.210%</t>
+          <t>-0.190%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -9288,32 +9288,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>159.56</v>
+        <v>159.602</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>159.223</v>
+        <v>159.2737</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9342,36 +9342,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>159.373</v>
+        <v>159.56</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>159.0204</v>
+        <v>159.223</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-0.220%</t>
+          <t>-0.210%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9396,46 +9396,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>159.499</v>
+        <v>159.373</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>159.1343</v>
+        <v>159.0204</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-0.230%</t>
+          <t>-0.220%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -9450,36 +9450,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>159.498</v>
+        <v>159.499</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>159.0963</v>
+        <v>159.1343</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-0.250%</t>
+          <t>-0.230%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -9504,36 +9504,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>159.275</v>
+        <v>159.498</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>158.8562</v>
+        <v>159.0963</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-0.260%</t>
+          <t>-0.250%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>159.231</v>
+        <v>159.275</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>158.8184</v>
+        <v>158.8562</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -9612,28 +9612,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>157.533</v>
+        <v>159.231</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>157.1215</v>
+        <v>158.8184</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9666,36 +9666,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>158.292</v>
+        <v>157.533</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>157.8532</v>
+        <v>157.1215</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>-0.280%</t>
+          <t>-0.260%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -9708,7 +9708,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -9718,36 +9720,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>157.661</v>
+        <v>158.292</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>157.1833</v>
+        <v>157.8532</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>-0.280%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -9770,36 +9772,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>157.725</v>
+        <v>157.661</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+0.38</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>157.2327</v>
+        <v>157.1833</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>-0.310%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -9822,28 +9824,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>156.772</v>
+        <v>157.725</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>+0.38</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>156.2866</v>
+        <v>157.2327</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -9874,36 +9876,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>158.878</v>
+        <v>156.772</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+0.41</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>158.3657</v>
+        <v>156.2866</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-0.320%</t>
+          <t>-0.310%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -9926,36 +9928,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>159.087</v>
+        <v>158.878</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>+0.41</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>158.554</v>
+        <v>158.3657</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>-0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-0.340%</t>
+          <t>-0.320%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -9978,36 +9980,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>163.329</v>
+        <v>159.087</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>162.7472</v>
+        <v>158.554</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>-0.58</v>
+        <v>-0.53</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>-0.360%</t>
+          <t>-0.340%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -10030,36 +10032,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>163.835</v>
+        <v>163.329</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>163.1987</v>
+        <v>162.7472</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>-0.64</v>
+        <v>-0.58</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-0.390%</t>
+          <t>-0.360%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -10082,28 +10084,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>163.763</v>
+        <v>163.835</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>163.1188</v>
+        <v>163.1987</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -10134,36 +10136,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>163.814</v>
+        <v>163.763</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>163.1588</v>
+        <v>163.1188</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>-0.400%</t>
+          <t>-0.390%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -10186,36 +10188,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>163.786</v>
+        <v>163.814</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+0.01</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>163.1055</v>
+        <v>163.1588</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>-0.68</v>
+        <v>-0.66</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>-0.420%</t>
+          <t>-0.400%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -10238,32 +10240,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>163.109</v>
+        <v>163.786</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+0.01</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>162.4168</v>
+        <v>163.1055</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -10290,36 +10292,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>163.194</v>
+        <v>163.109</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>162.4827</v>
+        <v>162.4168</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>-0.440%</t>
+          <t>-0.420%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -10342,36 +10344,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>162.485</v>
+        <v>163.194</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>161.7861</v>
+        <v>162.4827</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>-0.430%</t>
+          <t>-0.440%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -10386,6 +10388,58 @@
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>162.485</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>161.7861</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-0.430%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -10402,7 +10456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10484,15 +10538,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.324</v>
+        <v>1.3204</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -10501,11 +10555,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.3244</v>
+        <v>1.3208</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10538,15 +10592,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.3225</v>
+        <v>1.324</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -10555,11 +10609,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.3229</v>
+        <v>1.3244</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -10592,15 +10646,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.3216</v>
+        <v>1.3225</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -10609,11 +10663,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.322</v>
+        <v>1.3229</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -10629,9 +10683,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
@@ -10646,28 +10700,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.3274</v>
+        <v>1.3216</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.3278</v>
+        <v>1.322</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -10700,28 +10754,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3218</v>
+        <v>1.3274</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3223</v>
+        <v>1.3278</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -10729,7 +10783,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>+0.040%</t>
+          <t>+0.030%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -10754,28 +10808,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3239</v>
+        <v>1.3218</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.3244</v>
+        <v>1.3223</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -10808,28 +10862,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3189</v>
+        <v>1.3239</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.3195</v>
+        <v>1.3244</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -10862,15 +10916,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.326</v>
+        <v>1.3189</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -10879,11 +10933,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.3265</v>
+        <v>1.3195</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -10916,15 +10970,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3228</v>
+        <v>1.326</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -10933,11 +10987,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3233</v>
+        <v>1.3265</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -10970,15 +11024,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3258</v>
+        <v>1.3228</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -10987,11 +11041,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3264</v>
+        <v>1.3233</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -10999,7 +11053,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>+0.050%</t>
+          <t>+0.040%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11024,28 +11078,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3248</v>
+        <v>1.3258</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3255</v>
+        <v>1.3264</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -11061,9 +11115,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
@@ -11078,28 +11132,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3215</v>
+        <v>1.3248</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3222</v>
+        <v>1.3255</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -11132,28 +11186,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3242</v>
+        <v>1.3215</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3249</v>
+        <v>1.3222</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -11186,28 +11240,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3334</v>
+        <v>1.3242</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.334</v>
+        <v>1.3249</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -11240,15 +11294,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3368</v>
+        <v>1.3334</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -11257,11 +11311,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3374</v>
+        <v>1.334</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -11294,15 +11348,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3389</v>
+        <v>1.3368</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -11311,11 +11365,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.3397</v>
+        <v>1.3374</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -11323,7 +11377,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>+0.060%</t>
+          <t>+0.050%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11331,9 +11385,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Carry Richening (Elevated)</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
@@ -11341,22 +11395,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>⚠️ CARRY REGIME SHIFT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3353</v>
+        <v>1.3389</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -11365,11 +11419,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.336</v>
+        <v>1.3397</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -11377,7 +11431,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>+0.050%</t>
+          <t>+0.060%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11402,15 +11456,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3388</v>
+        <v>1.3353</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -11419,11 +11473,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.3394</v>
+        <v>1.336</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -11456,15 +11510,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3476</v>
+        <v>1.3388</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -11473,11 +11527,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.348</v>
+        <v>1.3394</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -11485,7 +11539,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>+0.030%</t>
+          <t>+0.050%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11510,15 +11564,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.351</v>
+        <v>1.3476</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -11527,11 +11581,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.3514</v>
+        <v>1.348</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -11564,15 +11618,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3524</v>
+        <v>1.351</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -11581,11 +11635,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.3526</v>
+        <v>1.3514</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -11593,7 +11647,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>+0.030%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11601,9 +11655,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Carry Richening (Elevated)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -11611,22 +11665,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3509</v>
+        <v>1.3524</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -11635,11 +11689,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.3511</v>
+        <v>1.3526</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -11672,15 +11726,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3542</v>
+        <v>1.3509</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -11689,11 +11743,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.3542</v>
+        <v>1.3511</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -11701,7 +11755,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11709,9 +11763,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
@@ -11726,28 +11780,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3546</v>
+        <v>1.3542</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.3547</v>
+        <v>1.3542</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -11755,7 +11809,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -11763,9 +11817,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
@@ -11780,36 +11834,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3514</v>
+        <v>1.3546</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.3514</v>
+        <v>1.3547</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -11817,9 +11871,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Carry Cheapening (Elevated)</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
@@ -11827,22 +11881,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>⚠️ CARRY REGIME SHIFT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3537</v>
+        <v>1.3514</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -11851,19 +11905,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.3538</v>
+        <v>1.3514</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>-0.000%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -11871,9 +11925,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
@@ -11881,22 +11935,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3484</v>
+        <v>1.3537</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -11905,11 +11959,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.3485</v>
+        <v>1.3538</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -11942,15 +11996,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3514</v>
+        <v>1.3484</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -11959,11 +12013,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.3515</v>
+        <v>1.3485</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -11979,9 +12033,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
@@ -11996,15 +12050,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3547</v>
+        <v>1.3514</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -12013,11 +12067,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.3548</v>
+        <v>1.3515</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -12033,9 +12087,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
@@ -12050,15 +12104,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3531</v>
+        <v>1.3547</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -12067,11 +12121,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.3532</v>
+        <v>1.3548</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -12104,15 +12158,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3587</v>
+        <v>1.3531</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -12121,11 +12175,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.3588</v>
+        <v>1.3532</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -12133,7 +12187,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -12158,28 +12212,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3591</v>
+        <v>1.3587</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.3591</v>
+        <v>1.3588</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -12212,15 +12266,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3644</v>
+        <v>1.3591</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -12229,11 +12283,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.3645</v>
+        <v>1.3591</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -12241,7 +12295,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12249,9 +12303,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
@@ -12266,28 +12320,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.3628</v>
+        <v>1.3644</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.3629</v>
+        <v>1.3645</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -12303,9 +12357,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
@@ -12320,15 +12374,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3649</v>
+        <v>1.3628</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -12337,11 +12391,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.3649</v>
+        <v>1.3629</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -12349,7 +12403,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -12357,9 +12411,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
@@ -12374,15 +12428,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3625</v>
+        <v>1.3649</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -12391,11 +12445,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.3626</v>
+        <v>1.3649</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -12403,7 +12457,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -12411,9 +12465,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
@@ -12428,15 +12482,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3603</v>
+        <v>1.3625</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -12445,11 +12499,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.3604</v>
+        <v>1.3626</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -12482,28 +12536,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3533</v>
+        <v>1.3603</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.3534</v>
+        <v>1.3604</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -12536,15 +12590,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.3537</v>
+        <v>1.3533</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -12553,11 +12607,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.3537</v>
+        <v>1.3534</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -12565,7 +12619,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -12590,28 +12644,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3532</v>
+        <v>1.3537</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.3532</v>
+        <v>1.3537</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -12627,9 +12681,9 @@
           <t>Structural: Future &gt; Spot</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
@@ -12644,28 +12698,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3484</v>
+        <v>1.3532</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.3484</v>
+        <v>1.3532</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -12678,12 +12732,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &gt; Spot</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -12698,15 +12752,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.3487</v>
+        <v>1.3484</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -12715,11 +12769,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.3488</v>
+        <v>1.3484</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -12727,7 +12781,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -12752,28 +12806,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.3502</v>
+        <v>1.3487</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.3502</v>
+        <v>1.3488</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -12781,7 +12835,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -12806,15 +12860,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.3506</v>
+        <v>1.3502</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -12823,11 +12877,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.3507</v>
+        <v>1.3502</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -12835,7 +12889,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -12860,15 +12914,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.3499</v>
+        <v>1.3506</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12877,11 +12931,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.3501</v>
+        <v>1.3507</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -12914,15 +12968,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.3458</v>
+        <v>1.3499</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12931,11 +12985,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.3458</v>
+        <v>1.3501</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -12943,7 +12997,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -12956,7 +13010,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -12966,15 +13022,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.3469</v>
+        <v>1.3458</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12983,11 +13039,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.3469</v>
+        <v>1.3458</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -13018,36 +13074,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.345</v>
+        <v>1.3469</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.3469</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>+0.13%</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1.3451</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -13070,28 +13126,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.3433</v>
+        <v>1.345</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.3433</v>
+        <v>1.3451</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -13099,7 +13155,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -13122,28 +13178,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.3485</v>
+        <v>1.3433</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.3486</v>
+        <v>1.3433</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -13151,7 +13207,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>+0.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -13174,28 +13230,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.3474</v>
+        <v>1.3485</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.3475</v>
+        <v>1.3486</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -13226,28 +13282,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.3361</v>
+        <v>1.3474</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.3362</v>
+        <v>1.3475</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -13278,28 +13334,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.329</v>
+        <v>1.3361</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.3291</v>
+        <v>1.3362</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -13330,15 +13386,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.3288</v>
+        <v>1.329</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -13347,11 +13403,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.3289</v>
+        <v>1.3291</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -13382,28 +13438,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.3326</v>
+        <v>1.3288</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.3327</v>
+        <v>1.3289</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -13434,15 +13490,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.3314</v>
+        <v>1.3326</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -13451,11 +13507,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.3316</v>
+        <v>1.3327</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -13486,15 +13542,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.3372</v>
+        <v>1.3314</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -13503,11 +13559,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.3374</v>
+        <v>1.3316</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -13538,15 +13594,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.3379</v>
+        <v>1.3372</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -13555,11 +13611,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.338</v>
+        <v>1.3374</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -13590,28 +13646,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.3433</v>
+        <v>1.3379</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.3434</v>
+        <v>1.338</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -13619,7 +13675,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>+0.010%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -13634,6 +13690,58 @@
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.3433</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1.3434</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
@@ -16790,7 +16898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16872,28 +16980,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8296</v>
+        <v>0.8347</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8236</v>
+        <v>0.8286</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16901,7 +17009,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-0.730%</t>
+          <t>-0.720%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -16926,28 +17034,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8314</v>
+        <v>0.8296</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8255</v>
+        <v>0.8236</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -16955,7 +17063,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-0.720%</t>
+          <t>-0.730%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -16963,9 +17071,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
@@ -16980,15 +17088,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8328</v>
+        <v>0.8314</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -16997,11 +17105,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8264</v>
+        <v>0.8255</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -17009,7 +17117,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0.770%</t>
+          <t>-0.720%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -17034,15 +17142,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8312</v>
+        <v>0.8328</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -17051,11 +17159,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8247</v>
+        <v>0.8264</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -17063,7 +17171,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0.780%</t>
+          <t>-0.770%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -17088,15 +17196,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8306</v>
+        <v>0.8312</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -17105,11 +17213,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.824</v>
+        <v>0.8247</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -17117,7 +17225,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0.800%</t>
+          <t>-0.780%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -17142,28 +17250,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8287</v>
+        <v>0.8306</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -17196,28 +17304,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8313</v>
+        <v>0.8287</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8245</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -17225,7 +17333,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0.820%</t>
+          <t>-0.800%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -17250,15 +17358,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8355</v>
+        <v>0.8313</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -17267,11 +17375,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8283</v>
+        <v>0.8245</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -17279,7 +17387,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0.860%</t>
+          <t>-0.820%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -17304,15 +17412,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8334</v>
+        <v>0.8355</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -17321,11 +17429,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8283</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -17333,7 +17441,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0.870%</t>
+          <t>-0.860%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -17358,15 +17466,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8318</v>
+        <v>0.8334</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -17375,11 +17483,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8245</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -17387,7 +17495,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0.880%</t>
+          <t>-0.870%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -17412,15 +17520,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8282</v>
+        <v>0.8318</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -17429,11 +17537,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8208</v>
+        <v>0.8245</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -17441,7 +17549,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>-0.880%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -17466,7 +17574,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -17474,20 +17582,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8206</v>
+        <v>0.8208</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -17495,7 +17603,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0.910%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -17520,28 +17628,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8243</v>
+        <v>0.8282</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8166</v>
+        <v>0.8206</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -17549,7 +17657,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0.940%</t>
+          <t>-0.910%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -17557,9 +17665,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Narrower)</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
@@ -17574,15 +17682,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8212</v>
+        <v>0.8243</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -17591,11 +17699,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8134</v>
+        <v>0.8166</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -17603,7 +17711,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0.950%</t>
+          <t>-0.940%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -17628,7 +17736,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -17636,7 +17744,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -17645,11 +17753,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8133</v>
+        <v>0.8134</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -17657,7 +17765,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0.960%</t>
+          <t>-0.950%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -17682,15 +17790,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.822</v>
+        <v>0.8212</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -17699,11 +17807,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8133</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -17711,7 +17819,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0.970%</t>
+          <t>-0.960%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -17736,15 +17844,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8246</v>
+        <v>0.822</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -17753,11 +17861,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8165</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -17765,7 +17873,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0.980%</t>
+          <t>-0.970%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -17790,15 +17898,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8246</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -17807,11 +17915,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8158</v>
+        <v>0.8165</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -17819,7 +17927,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1.020%</t>
+          <t>-0.980%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -17827,9 +17935,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Carry Cheapening (Elevated)</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Narrower)</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
@@ -17837,35 +17945,35 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>⚠️ CARRY REGIME SHIFT</t>
+          <t>Normal Trading</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8184</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8158</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -17898,28 +18006,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8162</v>
+        <v>0.8184</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8078</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -17927,7 +18035,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1.030%</t>
+          <t>-1.020%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -17952,15 +18060,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8167</v>
+        <v>0.8162</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -17969,19 +18077,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8165</v>
+        <v>0.8078</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-1.07%</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0.020%</t>
+          <t>-1.030%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -17989,9 +18097,9 @@
           <t>Structural: Future &lt; Spot</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Carry Drifting (Wider)</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Carry Cheapening (Elevated)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -17999,22 +18107,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Normal Trading</t>
+          <t>⚠️ CARRY REGIME SHIFT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8129</v>
+        <v>0.8167</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -18023,11 +18131,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8129</v>
+        <v>0.8165</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -18035,7 +18143,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0.010%</t>
+          <t>-0.020%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -18060,15 +18168,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8105</v>
+        <v>0.8129</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -18077,11 +18185,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8102</v>
+        <v>0.8129</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -18089,7 +18197,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0.040%</t>
+          <t>-0.010%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -18114,15 +18222,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8089</v>
+        <v>0.8105</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -18131,11 +18239,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8085</v>
+        <v>0.8102</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -18143,7 +18251,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0.050%</t>
+          <t>-0.040%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -18168,15 +18276,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -18185,11 +18293,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8095</v>
+        <v>0.8085</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -18197,7 +18305,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0.070%</t>
+          <t>-0.050%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -18222,15 +18330,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8068</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -18239,11 +18347,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8063</v>
+        <v>0.8095</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -18276,15 +18384,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8131</v>
+        <v>0.8068</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -18293,11 +18401,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8122</v>
+        <v>0.8063</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -18305,7 +18413,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0.110%</t>
+          <t>-0.070%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -18330,15 +18438,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8116</v>
+        <v>0.8131</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -18347,11 +18455,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8106</v>
+        <v>0.8122</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -18359,7 +18467,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0.130%</t>
+          <t>-0.110%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -18384,15 +18492,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8082</v>
+        <v>0.8116</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -18401,11 +18509,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8106</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -18413,7 +18521,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0.140%</t>
+          <t>-0.130%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -18438,15 +18546,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8096</v>
+        <v>0.8082</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -18455,11 +18563,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8084</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -18467,7 +18575,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0.150%</t>
+          <t>-0.140%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -18492,15 +18600,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8042</v>
+        <v>0.8096</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -18509,11 +18617,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8084</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -18521,7 +18629,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0.160%</t>
+          <t>-0.150%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -18546,15 +18654,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8053</v>
+        <v>0.8042</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -18563,11 +18671,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.8038</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -18575,7 +18683,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0.190%</t>
+          <t>-0.160%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -18600,15 +18708,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8053</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -18617,11 +18725,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8003</v>
+        <v>0.8038</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -18629,7 +18737,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-0.190%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -18654,28 +18762,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8025</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8008</v>
+        <v>0.8003</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -18683,7 +18791,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-0.210%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -18708,28 +18816,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8025</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.7991</v>
+        <v>0.8008</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -18737,7 +18845,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0.220%</t>
+          <t>-0.210%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -18762,15 +18870,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8008</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -18779,11 +18887,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7991</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -18791,7 +18899,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0.230%</t>
+          <t>-0.220%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -18816,15 +18924,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.798</v>
+        <v>0.8008</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -18833,11 +18941,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7958</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1.77%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -18845,7 +18953,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0.270%</t>
+          <t>-0.230%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -18870,15 +18978,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8125</v>
+        <v>0.798</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -18887,11 +18995,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8102</v>
+        <v>0.7958</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -18899,7 +19007,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-0.280%</t>
+          <t>-0.270%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -18924,15 +19032,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8115</v>
+        <v>0.8125</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -18941,11 +19049,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8092</v>
+        <v>0.8102</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -18978,15 +19086,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8115</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -18995,11 +19103,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.8106</v>
+        <v>0.8092</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -19007,7 +19115,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>-0.280%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -19032,15 +19140,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8139</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -19049,11 +19157,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.8114</v>
+        <v>0.8106</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -19061,17 +19169,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-0.310%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Structural: Flat</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Normal Carry Range</t>
+          <t>Structural: Future &lt; Spot</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Carry Drifting (Wider)</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -19086,15 +19194,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8136</v>
+        <v>0.8139</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -19103,11 +19211,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.8109</v>
+        <v>0.8114</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -19115,7 +19223,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-0.340%</t>
+          <t>-0.310%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -19140,15 +19248,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8112</v>
+        <v>0.8136</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -19157,11 +19265,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8083</v>
+        <v>0.8109</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -19169,7 +19277,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-0.360%</t>
+          <t>-0.340%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -19194,15 +19302,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8102</v>
+        <v>0.8112</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -19211,11 +19319,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.8072</v>
+        <v>0.8083</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -19223,7 +19331,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>-0.370%</t>
+          <t>-0.360%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -19248,15 +19356,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8073</v>
+        <v>0.8102</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -19265,11 +19373,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.8043</v>
+        <v>0.8072</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -19302,28 +19410,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8119</v>
+        <v>0.8073</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.8088</v>
+        <v>0.8043</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -19331,7 +19439,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>-0.380%</t>
+          <t>-0.370%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -19344,7 +19452,9 @@
           <t>Normal Carry Range</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>Normal Trading</t>
@@ -19354,28 +19464,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8068</v>
+        <v>0.8119</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.8035</v>
+        <v>0.8088</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -19383,7 +19493,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>-0.410%</t>
+          <t>-0.380%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -19406,15 +19516,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8092</v>
+        <v>0.8068</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -19423,11 +19533,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.8057</v>
+        <v>0.8035</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -19435,7 +19545,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>-0.430%</t>
+          <t>-0.410%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -19458,15 +19568,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8099</v>
+        <v>0.8092</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -19475,11 +19585,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8064</v>
+        <v>0.8057</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -19510,28 +19620,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8079</v>
+        <v>0.8099</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8042</v>
+        <v>0.8064</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -19539,7 +19649,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-0.450%</t>
+          <t>-0.430%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -19562,28 +19672,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>0.8042</v>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>-1.27%</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0.8005</v>
-      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -19591,7 +19701,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-0.460%</t>
+          <t>-0.450%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -19614,15 +19724,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8145</v>
+        <v>0.8042</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -19631,11 +19741,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8105</v>
+        <v>0.8005</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -19643,7 +19753,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>-0.490%</t>
+          <t>-0.460%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -19666,15 +19776,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8189</v>
+        <v>0.8145</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -19683,11 +19793,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8147</v>
+        <v>0.8105</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -19695,7 +19805,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-0.510%</t>
+          <t>-0.490%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -19718,15 +19828,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.819</v>
+        <v>0.8189</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -19739,7 +19849,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -19747,7 +19857,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>-0.530%</t>
+          <t>-0.510%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -19770,15 +19880,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8181</v>
+        <v>0.819</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -19787,11 +19897,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8137</v>
+        <v>0.8147</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -19822,15 +19932,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8169</v>
+        <v>0.8181</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -19839,11 +19949,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8124</v>
+        <v>0.8137</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -19851,7 +19961,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>-0.550%</t>
+          <t>-0.530%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -19874,15 +19984,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8145</v>
+        <v>0.8169</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -19891,11 +20001,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8098</v>
+        <v>0.8124</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -19903,7 +20013,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>-0.570%</t>
+          <t>-0.550%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -19926,15 +20036,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8128</v>
+        <v>0.8145</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -19943,11 +20053,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8098</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -19955,7 +20065,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>-0.590%</t>
+          <t>-0.570%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -19978,28 +20088,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8099</v>
+        <v>0.8128</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8051</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -20022,6 +20132,58 @@
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" t="inlineStr">
+        <is>
+          <t>Normal Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-0.590%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Structural: Flat</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Normal Carry Range</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Normal Trading</t>
         </is>
